--- a/data/trans_bre/P1417-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P1417-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,93</t>
+          <t>2,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -665,17 +665,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,23</t>
+          <t>0,23; 2,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,37</t>
+          <t>-0,27; 2,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,7; 8,5</t>
+          <t>0,8; 6,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-97,68; —</t>
+          <t>-72,8; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,16</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,64</t>
+          <t>0,52; 2,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,04</t>
+          <t>0,75; 3,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,69; 3,12</t>
+          <t>0,83; 3,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,96</t>
+          <t>1,17; 4,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4,56</t>
+          <t>4,83</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>435,05%</t>
+          <t>522,4%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,93</t>
+          <t>0,66; 2,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 5,42</t>
+          <t>2,55; 5,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,17</t>
+          <t>0,82; 3,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,52</t>
+          <t>3,22; 6,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>96,51; 1398,78</t>
+          <t>148,3; 1630,18</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,06</t>
+          <t>5,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1628,31%</t>
+          <t>979,67%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,25</t>
+          <t>0,05; 2,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,84</t>
+          <t>0,72; 3,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,28</t>
+          <t>0,49; 3,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,61; 6,54</t>
+          <t>3,83; 6,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,69; —</t>
+          <t>-43,99; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>27,91; 2378,09</t>
+          <t>36,49; 1833,68</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,76; 1868,92</t>
+          <t>17,73; 2371,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>407,87; 9377,89</t>
+          <t>299,98; 3579,31</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,25</t>
+          <t>1,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87,53%</t>
+          <t>68,26%</t>
         </is>
       </c>
     </row>
@@ -1060,22 +1060,22 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,17</t>
+          <t>1,03; 4,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,75</t>
+          <t>0,66; 3,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,05</t>
+          <t>0,75; 3,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 2,59</t>
+          <t>-0,17; 2,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1085,17 +1085,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,79; —</t>
+          <t>-2,99; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,08; —</t>
+          <t>19,09; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 267,93</t>
+          <t>-13,38; 272,92</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-0,66</t>
+          <t>0,47</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-23,56%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 2,27</t>
+          <t>-1,76; 2,43</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 3,41</t>
+          <t>-1,36; 3,49</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,73</t>
+          <t>-0,69; 3,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 1,08</t>
+          <t>-1,31; 2,27</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 552,65</t>
+          <t>-71,77; 564,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-51,56; 329,92</t>
+          <t>-49,93; 366,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-33,09; 654,54</t>
+          <t>-42,88; 633,62</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,43; 46,83</t>
+          <t>-39,45; 133,66</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>4,14</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>101,26%</t>
+          <t>94,44%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 4,35</t>
+          <t>-1,76; 4,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 5,62</t>
+          <t>0,84; 5,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 5,88</t>
+          <t>0,24; 5,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,54; 7,1</t>
+          <t>1,3; 6,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-53,35; 647,54</t>
+          <t>-54,43; 586,11</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; —</t>
+          <t>-10,73; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 825,97</t>
+          <t>-3,08; 930,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,88; 248,84</t>
+          <t>20,88; 231,78</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>273,35%</t>
+          <t>264,28%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,83</t>
+          <t>0,8; 1,82</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,72; 2,97</t>
+          <t>1,71; 2,91</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,33; 2,51</t>
+          <t>1,32; 2,5</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,86</t>
+          <t>2,6; 3,89</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>119,47; 735,4</t>
+          <t>125,2; 667,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>268,3; 1093,33</t>
+          <t>267,68; 970,2</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>168,04; 658,49</t>
+          <t>167,1; 647,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>157,51; 425,18</t>
+          <t>164,03; 383,6</t>
         </is>
       </c>
     </row>
